--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2015/OKLAHOMA_2015.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2015/OKLAHOMA_2015.xlsx
@@ -2742,7 +2742,7 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Cuatro Cienegas</t>
+          <t>Cuatrocienegas</t>
         </is>
       </c>
       <c r="C133">
@@ -3588,7 +3588,7 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>General Simon Bolivar</t>
+          <t>Gral. Simon Bolivar</t>
         </is>
       </c>
       <c r="C180">
@@ -5557,7 +5557,7 @@
         <v>15</v>
       </c>
       <c r="D289">
-        <v>0.0009654994850669413</v>
+        <v>0.0009654994850669412</v>
       </c>
     </row>
     <row r="290">
@@ -5766,7 +5766,7 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C301">
@@ -9517,7 +9517,7 @@
         <v>15</v>
       </c>
       <c r="D509">
-        <v>0.0009654994850669413</v>
+        <v>0.0009654994850669412</v>
       </c>
     </row>
     <row r="510">
@@ -12354,7 +12354,7 @@
       </c>
       <c r="B667" t="inlineStr">
         <is>
-          <t>General Escobedo</t>
+          <t>Gral. Escobedo</t>
         </is>
       </c>
       <c r="C667">
@@ -12451,7 +12451,7 @@
         <v>15</v>
       </c>
       <c r="D672">
-        <v>0.0009654994850669413</v>
+        <v>0.0009654994850669412</v>
       </c>
     </row>
     <row r="673">
@@ -16465,7 +16465,7 @@
         <v>15</v>
       </c>
       <c r="D895">
-        <v>0.0009654994850669413</v>
+        <v>0.0009654994850669412</v>
       </c>
     </row>
     <row r="896">
@@ -17779,7 +17779,7 @@
         <v>15</v>
       </c>
       <c r="D968">
-        <v>0.0009654994850669413</v>
+        <v>0.0009654994850669412</v>
       </c>
     </row>
     <row r="969">
@@ -18265,7 +18265,7 @@
         <v>15</v>
       </c>
       <c r="D995">
-        <v>0.0009654994850669413</v>
+        <v>0.0009654994850669412</v>
       </c>
     </row>
     <row r="996">
@@ -18931,7 +18931,7 @@
         <v>15</v>
       </c>
       <c r="D1032">
-        <v>0.0009654994850669413</v>
+        <v>0.0009654994850669412</v>
       </c>
     </row>
     <row r="1033">
@@ -21793,7 +21793,7 @@
         <v>15</v>
       </c>
       <c r="D1191">
-        <v>0.0009654994850669413</v>
+        <v>0.0009654994850669412</v>
       </c>
     </row>
     <row r="1192">
